--- a/outputs/263-1.xlsx
+++ b/outputs/263-1.xlsx
@@ -373,7 +373,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <f aca="false">SUMPRODUCT((A2:A1000=G2)*(B2:B1000)*(C2:C1000))</f>
+        <f aca="false">SUMPRODUCT(($A$2:$A$276=$G2)*$B$2:$B$276*$C$2:$C$276)</f>
         <v>3710</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -394,7 +394,7 @@
         <v>7</v>
       </c>
       <c r="H3" s="2" t="n">
-        <f aca="false">SUMPRODUCT((A2:A1000=G3)*(B2:B1000)*(C2:C1000))</f>
+        <f aca="false">SUMPRODUCT(($A$2:$A$276=$G3)*$B$2:$B$276*$C$2:$C$276)</f>
         <v>1660</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -415,7 +415,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="2" t="n">
-        <f aca="false">SUMPRODUCT((A2:A1000=G4)*(B2:B1000)*(C2:C1000))</f>
+        <f aca="false">SUMPRODUCT(($A$2:$A$276=$G4)*$B$2:$B$276*$C$2:$C$276)</f>
         <v>2753</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -435,10 +435,7 @@
       <c r="G5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <f aca="false">SUMPRODUCT((A2:A1000=G5)*(B2:B1000)*(C2:C1000))</f>
-        <v>3514</v>
-      </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
         <v>6</v>
       </c>
